--- a/data/trans_dic/P6907S1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 12,04</t>
+          <t>3,27; 12,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,83</t>
+          <t>0,0; 19,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 15,91</t>
+          <t>1,79; 16,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>0,0; 18,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 19,94</t>
+          <t>2,14; 21,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,98</t>
+          <t>0,0; 15,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,02</t>
+          <t>3,87; 11,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,22</t>
+          <t>0,0; 11,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,57; 12,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,28</t>
+          <t>1,34; 12,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,08</t>
+          <t>6,06; 13,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 13,01</t>
+          <t>2,15; 12,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,98</t>
+          <t>1,28; 5,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 13,61</t>
+          <t>5,97; 13,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 14,43</t>
+          <t>4,18; 14,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,55</t>
+          <t>3,99; 10,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,69</t>
+          <t>6,25; 12,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,17</t>
+          <t>1,31; 8,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,76</t>
+          <t>1,17; 4,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,88</t>
+          <t>5,82; 10,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 23,72</t>
+          <t>6,05; 23,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,24</t>
+          <t>0,0; 10,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 30,72</t>
+          <t>8,98; 31,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 27,59</t>
+          <t>8,25; 28,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,12</t>
+          <t>6,0; 47,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 13,0</t>
+          <t>1,24; 12,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 24,34</t>
+          <t>7,86; 22,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,93; 21,88</t>
+          <t>9,32; 23,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 21,63</t>
+          <t>2,66; 23,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,64</t>
+          <t>1,35; 8,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 22,55</t>
+          <t>9,99; 22,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,13</t>
+          <t>6,84; 12,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 9,72</t>
+          <t>2,6; 10,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,89</t>
+          <t>1,94; 6,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 15,16</t>
+          <t>7,75; 15,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,58</t>
+          <t>7,24; 16,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,73</t>
+          <t>0,86; 7,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,44</t>
+          <t>0,88; 5,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,6</t>
+          <t>5,4; 11,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,22</t>
+          <t>7,53; 12,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,57</t>
+          <t>2,25; 7,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,85</t>
+          <t>1,95; 4,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 12,29</t>
+          <t>6,95; 11,89</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3557; 13403</t>
+          <t>3639; 14380</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7124</t>
+          <t>0; 6152</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1021; 8843</t>
+          <t>995; 8975</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5048</t>
+          <t>0; 5457</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>867; 7492</t>
+          <t>803; 8245</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1952</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1800</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3243</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6008; 17897</t>
+          <t>5760; 17481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6975</t>
+          <t>0; 6232</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 9211</t>
+          <t>423; 9022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>734; 6658</t>
+          <t>725; 6675</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16352; 37524</t>
+          <t>17394; 38345</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1999; 12150</t>
+          <t>2007; 11786</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3029; 13707</t>
+          <t>2931; 13117</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15123; 32613</t>
+          <t>14306; 33191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5009; 17108</t>
+          <t>4962; 17171</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2014</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5928</t>
+          <t>0; 6232</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8899; 25151</t>
+          <t>9507; 24802</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25577; 51456</t>
+          <t>25345; 50079</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2191; 12881</t>
+          <t>2070; 12634</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4238; 16838</t>
+          <t>4159; 16039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27358; 52023</t>
+          <t>27826; 52543</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4737; 17568</t>
+          <t>4479; 17105</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2005</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6504</t>
+          <t>0; 6525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6434; 21358</t>
+          <t>6244; 21916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5288; 17653</t>
+          <t>5277; 18279</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6634</t>
+          <t>864; 6777</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>929; 9584</t>
+          <t>917; 9258</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6946; 22072</t>
+          <t>7125; 20764</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12325; 30214</t>
+          <t>12872; 32143</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>832; 7002</t>
+          <t>861; 7569</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1959; 11859</t>
+          <t>1851; 11904</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15861; 36128</t>
+          <t>16002; 36803</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31374; 57283</t>
+          <t>32292; 57892</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3828; 13864</t>
+          <t>3708; 15108</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6254; 20520</t>
+          <t>6766; 21679</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25830; 51278</t>
+          <t>26211; 51477</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16145; 34298</t>
+          <t>15931; 35361</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>901; 7739</t>
+          <t>865; 7292</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1873; 11770</t>
+          <t>1914; 12838</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19176; 41055</t>
+          <t>19127; 40206</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52223; 84638</t>
+          <t>52127; 84594</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5690; 18377</t>
+          <t>5467; 18786</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10224; 27415</t>
+          <t>10986; 27311</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50861; 85123</t>
+          <t>48108; 82323</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6907S1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 12,92</t>
+          <t>3,26; 12,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,72</t>
+          <t>0,0; 19,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 16,15</t>
+          <t>1,81; 16,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,68</t>
+          <t>0,0; 14,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 21,95</t>
+          <t>2,29; 20,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,68</t>
+          <t>0,0; 17,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 11,74</t>
+          <t>3,86; 11,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,81</t>
+          <t>0,0; 11,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 12,26</t>
+          <t>1,38; 12,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 12,31</t>
+          <t>1,27; 11,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 13,36</t>
+          <t>5,91; 13,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,62</t>
+          <t>2,15; 12,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,72</t>
+          <t>1,28; 6,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 13,85</t>
+          <t>5,88; 13,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 14,48</t>
+          <t>4,16; 14,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,4</t>
+          <t>5,13; 12,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,35</t>
+          <t>6,25; 12,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,02</t>
+          <t>1,28; 7,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,53</t>
+          <t>1,32; 4,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,99</t>
+          <t>6,53; 11,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 23,09</t>
+          <t>6,26; 22,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,27</t>
+          <t>0,0; 10,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 31,52</t>
+          <t>9,01; 31,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 28,57</t>
+          <t>8,21; 26,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 47,11</t>
+          <t>5,93; 46,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,56</t>
+          <t>1,26; 12,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 22,89</t>
+          <t>6,74; 20,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,32; 23,28</t>
+          <t>8,77; 21,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 23,38</t>
+          <t>2,65; 21,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,67</t>
+          <t>1,42; 8,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 22,97</t>
+          <t>9,87; 22,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,26</t>
+          <t>6,61; 12,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,6</t>
+          <t>2,62; 10,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,22</t>
+          <t>1,8; 5,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 15,22</t>
+          <t>7,3; 14,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 16,06</t>
+          <t>7,03; 15,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,28</t>
+          <t>0,88; 7,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,94</t>
+          <t>0,81; 5,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,36</t>
+          <t>6,84; 13,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,22</t>
+          <t>7,72; 12,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,74</t>
+          <t>2,42; 7,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,84</t>
+          <t>1,91; 4,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 11,89</t>
+          <t>7,8; 12,74</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2983</t>
         </is>
       </c>
     </row>
@@ -1504,27 +1504,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3639; 14380</t>
+          <t>3630; 13687</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6152</t>
+          <t>0; 6138</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>995; 8975</t>
+          <t>1006; 9268</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5457</t>
+          <t>0; 5371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>803; 8245</t>
+          <t>862; 7875</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1539,27 +1539,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3917</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5760; 17481</t>
+          <t>5748; 17612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6232</t>
+          <t>0; 6185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>423; 9022</t>
+          <t>1013; 8894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>725; 6675</t>
+          <t>773; 6977</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22403</t>
+          <t>24525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>42156</t>
         </is>
       </c>
     </row>
@@ -1712,27 +1712,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17394; 38345</t>
+          <t>16965; 38000</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2007; 11786</t>
+          <t>2006; 11843</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2931; 13117</t>
+          <t>2945; 14502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14306; 33191</t>
+          <t>15862; 36949</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4962; 17171</t>
+          <t>4935; 17173</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6232</t>
+          <t>0; 6818</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9507; 24802</t>
+          <t>11332; 26676</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25345; 50079</t>
+          <t>25357; 49058</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2070; 12634</t>
+          <t>2011; 11185</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4159; 16039</t>
+          <t>4656; 17103</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27826; 52543</t>
+          <t>32043; 56544</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24472</t>
+          <t>26211</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4479; 17105</t>
+          <t>4637; 16770</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1930,52 +1930,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6525</t>
+          <t>0; 6547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6244; 21916</t>
+          <t>7010; 24314</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5277; 18279</t>
+          <t>5253; 17237</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>864; 6777</t>
+          <t>853; 6622</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>917; 9258</t>
+          <t>932; 9202</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7125; 20764</t>
+          <t>6700; 20316</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12872; 32143</t>
+          <t>12112; 29680</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>861; 7569</t>
+          <t>858; 7008</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1851; 11904</t>
+          <t>1945; 11539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16002; 36803</t>
+          <t>17490; 40088</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>39513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>71351</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32292; 57892</t>
+          <t>31212; 58423</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3708; 15108</t>
+          <t>3736; 14741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6766; 21679</t>
+          <t>6284; 20056</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26211; 51477</t>
+          <t>28017; 56872</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15931; 35361</t>
+          <t>15468; 33934</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>865; 7292</t>
+          <t>881; 7526</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1914; 12838</t>
+          <t>1754; 11305</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19127; 40206</t>
+          <t>23588; 45144</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52127; 84594</t>
+          <t>53477; 84837</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5467; 18786</t>
+          <t>5871; 19125</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10986; 27311</t>
+          <t>10815; 28083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>48108; 82323</t>
+          <t>56824; 92826</t>
         </is>
       </c>
     </row>
